--- a/Группы движкимого имущества (параметры).xlsx
+++ b/Группы движкимого имущества (параметры).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Личные папки\Никита Шулин\!Работа\16. Проект (мега-тендер)\9. Мои работы по проекту из августа 2026\Проект - информация и методология\2. Движимое имущество\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31F701D-4BA0-46B2-A02B-ECA0E3DCEE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624EB945-8354-4120-94B1-CB4696349B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="329">
   <si>
     <t>Класс</t>
   </si>
@@ -852,17 +852,236 @@
     <t>Комплектность (сканер, денежный ящик, принтер чеков и т.д.)</t>
   </si>
   <si>
-    <t>инвентарь и хозяйственные принадлежности</t>
-  </si>
-  <si>
-    <t>нематериальные компоненты движимого имущества</t>
+    <t>Нематериальные компоненты движимого имущества</t>
+  </si>
+  <si>
+    <t>Встроенное и системное программное обеспечение</t>
+  </si>
+  <si>
+    <t>Наименование и версия программного обеспечения</t>
+  </si>
+  <si>
+    <t>Тип и номер лицензии (при наличии) / способ использования (лицензионное, свободно распространяемое, встроенное неотчуждаемое от оборудования)</t>
+  </si>
+  <si>
+    <t>Оборудование (носитель), с которым ПО функционально связано</t>
+  </si>
+  <si>
+    <t>Срок действия лицензии (бессрочная/ограниченная, дата окончания)</t>
+  </si>
+  <si>
+    <t>Возможность автономного использования/передачи отдельно от оборудования</t>
+  </si>
+  <si>
+    <t>Прикладное программное обеспечение и цифровые лицензии</t>
+  </si>
+  <si>
+    <t>операционные системы, установленные на оборудование (ПК, серверы, станки с ЧПУ)</t>
+  </si>
+  <si>
+    <t>встроенное программное обеспечение (firmware/прошивка) технологического оборудования</t>
+  </si>
+  <si>
+    <t>системы числового программного управления (ЧПУ, PLC-контроллеры)</t>
+  </si>
+  <si>
+    <t>SCADA-системы и системы автоматизации технологических процессов</t>
+  </si>
+  <si>
+    <t>офисное и специализированное прикладное ПО (бухгалтерское, инженерное, CAD/CAM, аналитическое)</t>
+  </si>
+  <si>
+    <t>корпоративные информационные системы (ERP, CRM)</t>
+  </si>
+  <si>
+    <t>ключи активации, электронные лицензии, подписки (SaaS)</t>
+  </si>
+  <si>
+    <t>Тип и номер лицензии (per-user, per-device, серверная, корпоративная и т.д.)</t>
+  </si>
+  <si>
+    <t>Количество лицензированных пользователей/устройств (если применимо)</t>
+  </si>
+  <si>
+    <t>Срок действия лицензии / периодичность продления (для подписочных моделей)</t>
+  </si>
+  <si>
+    <t>Наличие технической поддержки/обновлений в рамках лицензии</t>
+  </si>
+  <si>
+    <t>Технологические базы данных и конфигурации</t>
+  </si>
+  <si>
+    <t>технологические программы обработки (управляющие программы для станков с ЧПУ)</t>
+  </si>
+  <si>
+    <t>базы данных технологических параметров, рецептур, настроек оборудования</t>
+  </si>
+  <si>
+    <t>индивидуальные конфигурации и настройки систем автоматизации</t>
+  </si>
+  <si>
+    <t>Наименование и назначение (для какого оборудования/процесса разработано)</t>
+  </si>
+  <si>
+    <t>Носитель хранения (встроенная память оборудования, отдельный сервер, внешний носитель)</t>
+  </si>
+  <si>
+    <t>Уникальность/оригинальность (разработано индивидуально под объект либо является типовым продуктом)</t>
+  </si>
+  <si>
+    <t>Возможность переноса на аналогичное оборудование</t>
+  </si>
+  <si>
+    <t>Наличие резервной копии / документации по восстановлению</t>
+  </si>
+  <si>
+    <t>Спецтехника</t>
+  </si>
+  <si>
+    <t>Экскаваторы (гусеничные, колёсные)</t>
+  </si>
+  <si>
+    <t>Бульдозеры</t>
+  </si>
+  <si>
+    <t>Автогрейдеры</t>
+  </si>
+  <si>
+    <t>Самосвалы карьерные</t>
+  </si>
+  <si>
+    <t>Автобетоносмесители</t>
+  </si>
+  <si>
+    <t>Строительная спецтехника</t>
+  </si>
+  <si>
+    <t>Марка (модель) и заводской/серийный номер (VIN)</t>
+  </si>
+  <si>
+    <t>Эксплуатационная масса / грузоподъёмность (т)</t>
+  </si>
+  <si>
+    <t>Наработка (моточасы/пробег)</t>
+  </si>
+  <si>
+    <t>Тип ходовой части (гусеничная/колёсная)</t>
+  </si>
+  <si>
+    <t>Коммунальная спецтехника</t>
+  </si>
+  <si>
+    <t>Буровые установки</t>
+  </si>
+  <si>
+    <t>Мусоровозы</t>
+  </si>
+  <si>
+    <t>Поливомоечные машины</t>
+  </si>
+  <si>
+    <t>Снегоуборочная техника</t>
+  </si>
+  <si>
+    <t>Вакуумные илососы</t>
+  </si>
+  <si>
+    <t>Подметально-уборочные машины</t>
+  </si>
+  <si>
+    <t>Объём кузова/цистерны/бункера (м³)</t>
+  </si>
+  <si>
+    <t>Наличие сменного/навесного оборудования</t>
+  </si>
+  <si>
+    <t>Сельскохозяйственная спецтехника</t>
+  </si>
+  <si>
+    <t>Тракторы</t>
+  </si>
+  <si>
+    <t>Зерноуборочные и кормоуборочные комбайны</t>
+  </si>
+  <si>
+    <t>Прицепная и навесная сельхозтехника (плуги, сеялки, опрыскиватели)</t>
+  </si>
+  <si>
+    <t>Самоходные опрыскиватели</t>
+  </si>
+  <si>
+    <t>Производительность / ширина захвата (га/ч, м)</t>
+  </si>
+  <si>
+    <t>Наработка (моточасы)</t>
+  </si>
+  <si>
+    <t>Тип агрегатирования (навесное, прицепное, самоходное)</t>
+  </si>
+  <si>
+    <t>Погрузочно-разгрузочная спецтехника</t>
+  </si>
+  <si>
+    <t>Вилочные погрузчики (дизельные, электрические, газовые)</t>
+  </si>
+  <si>
+    <t>Фронтальные погрузчики</t>
+  </si>
+  <si>
+    <t>Телескопические погрузчики</t>
+  </si>
+  <si>
+    <t>Тип питания (дизель/электро/газ)</t>
+  </si>
+  <si>
+    <t>Грузоподъёмная самоходная спецтехника</t>
+  </si>
+  <si>
+    <t>Автокраны</t>
+  </si>
+  <si>
+    <t>Автовышки (телескопические, коленчатые)</t>
+  </si>
+  <si>
+    <t>Манипуляторы (краны-манипуляторы на шасси)</t>
+  </si>
+  <si>
+    <t>Максимальный вылет стрелы / высота подъёма (м)</t>
+  </si>
+  <si>
+    <r>
+      <t>Объём двигателя (см</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)/ мощность двигателя (л.с. / кВт)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -888,8 +1107,17 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -905,12 +1133,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -987,6 +1209,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -997,9 +1222,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1307,37 +1529,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="16"/>
-      <c r="G1" s="17" t="s">
+      <c r="F1" s="17"/>
+      <c r="G1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="18" t="s">
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="18"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="15"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
@@ -4973,416 +5195,908 @@
         <v>261</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A127" s="5"/>
-      <c r="B127" s="4"/>
-      <c r="C127" s="4"/>
-      <c r="D127" s="10"/>
+    <row r="127" spans="1:11" ht="57" x14ac:dyDescent="0.2">
+      <c r="A127" s="5">
+        <v>8</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D127" s="10" t="s">
+        <v>270</v>
+      </c>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
-      <c r="G127" s="4"/>
-      <c r="H127" s="4"/>
-      <c r="I127" s="4"/>
-      <c r="J127" s="4"/>
-      <c r="K127" s="4"/>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G127" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="J127" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="K127" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="57" x14ac:dyDescent="0.2">
       <c r="A128" s="5"/>
-      <c r="B128" s="4"/>
-      <c r="C128" s="4"/>
-      <c r="D128" s="10"/>
+      <c r="B128" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D128" s="10" t="s">
+        <v>271</v>
+      </c>
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
-      <c r="G128" s="4"/>
-      <c r="H128" s="4"/>
-      <c r="I128" s="4"/>
-      <c r="J128" s="4"/>
-      <c r="K128" s="4"/>
-    </row>
-    <row r="129" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A129" s="5">
-        <v>8</v>
-      </c>
-      <c r="B129" s="19" t="s">
+      <c r="G128" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I128" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="J128" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="K128" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="57" x14ac:dyDescent="0.2">
+      <c r="A129" s="15"/>
+      <c r="B129" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C129" s="4"/>
-      <c r="D129" s="10"/>
+      <c r="C129" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D129" s="10" t="s">
+        <v>272</v>
+      </c>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
-      <c r="G129" s="4"/>
-      <c r="H129" s="4"/>
-      <c r="I129" s="4"/>
-      <c r="J129" s="4"/>
-      <c r="K129" s="4"/>
-    </row>
-    <row r="130" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A130" s="5">
-        <v>9</v>
-      </c>
-      <c r="B130" s="19" t="s">
+      <c r="G129" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I129" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="J129" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="K129" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" ht="57" x14ac:dyDescent="0.2">
+      <c r="A130" s="15"/>
+      <c r="B130" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C130" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="C130" s="4"/>
-      <c r="D130" s="10"/>
+      <c r="D130" s="10" t="s">
+        <v>273</v>
+      </c>
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
-      <c r="G130" s="4"/>
-      <c r="H130" s="4"/>
-      <c r="I130" s="4"/>
-      <c r="J130" s="4"/>
-      <c r="K130" s="4"/>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A131" s="5"/>
-      <c r="B131" s="19"/>
-      <c r="C131" s="4"/>
-      <c r="D131" s="10"/>
+      <c r="G130" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I130" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="J130" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="K130" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="57" x14ac:dyDescent="0.2">
+      <c r="A131" s="15"/>
+      <c r="B131" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>274</v>
+      </c>
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
-      <c r="G131" s="4"/>
-      <c r="H131" s="4"/>
-      <c r="I131" s="4"/>
-      <c r="J131" s="4"/>
-      <c r="K131" s="4"/>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G131" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I131" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="J131" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="K131" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A132" s="5"/>
-      <c r="B132" s="4"/>
-      <c r="C132" s="4"/>
-      <c r="D132" s="10"/>
+      <c r="B132" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D132" s="10" t="s">
+        <v>275</v>
+      </c>
       <c r="E132" s="4"/>
       <c r="F132" s="4"/>
-      <c r="G132" s="4"/>
-      <c r="H132" s="4"/>
-      <c r="I132" s="4"/>
-      <c r="J132" s="4"/>
-      <c r="K132" s="4"/>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G132" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I132" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="J132" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="K132" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A133" s="5"/>
-      <c r="B133" s="4"/>
-      <c r="C133" s="4"/>
-      <c r="D133" s="10"/>
+      <c r="B133" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>276</v>
+      </c>
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
-      <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
-      <c r="I133" s="4"/>
-      <c r="J133" s="4"/>
-      <c r="K133" s="4"/>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G133" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I133" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="J133" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="K133" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A134" s="5"/>
-      <c r="B134" s="4"/>
-      <c r="C134" s="4"/>
-      <c r="D134" s="10"/>
+      <c r="B134" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D134" s="10" t="s">
+        <v>282</v>
+      </c>
       <c r="E134" s="4"/>
       <c r="F134" s="4"/>
-      <c r="G134" s="4"/>
-      <c r="H134" s="4"/>
-      <c r="I134" s="4"/>
-      <c r="J134" s="4"/>
-      <c r="K134" s="4"/>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G134" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I134" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="J134" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="K134" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A135" s="5"/>
-      <c r="B135" s="4"/>
-      <c r="C135" s="4"/>
-      <c r="D135" s="10"/>
+      <c r="B135" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D135" s="10" t="s">
+        <v>283</v>
+      </c>
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
-      <c r="G135" s="4"/>
-      <c r="H135" s="4"/>
-      <c r="I135" s="4"/>
-      <c r="J135" s="4"/>
-      <c r="K135" s="4"/>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G135" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I135" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="J135" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="K135" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A136" s="5"/>
-      <c r="B136" s="4"/>
-      <c r="C136" s="4"/>
-      <c r="D136" s="10"/>
+      <c r="B136" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>284</v>
+      </c>
       <c r="E136" s="4"/>
       <c r="F136" s="4"/>
-      <c r="G136" s="4"/>
-      <c r="H136" s="4"/>
-      <c r="I136" s="4"/>
-      <c r="J136" s="4"/>
-      <c r="K136" s="4"/>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A137" s="5"/>
-      <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
-      <c r="D137" s="10"/>
+      <c r="G136" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="H136" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I136" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="J136" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="K136" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
+      <c r="A137" s="5">
+        <v>9</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>291</v>
+      </c>
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
-      <c r="J137" s="4"/>
-      <c r="K137" s="4"/>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G137" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I137" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="J137" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K137" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A138" s="5"/>
-      <c r="B138" s="4"/>
-      <c r="C138" s="4"/>
-      <c r="D138" s="10"/>
+      <c r="B138" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>292</v>
+      </c>
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
-      <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="4"/>
-      <c r="K138" s="4"/>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G138" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H138" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I138" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="J138" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K138" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A139" s="5"/>
-      <c r="B139" s="4"/>
-      <c r="C139" s="4"/>
-      <c r="D139" s="10"/>
+      <c r="B139" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>293</v>
+      </c>
       <c r="E139" s="4"/>
       <c r="F139" s="4"/>
-      <c r="G139" s="4"/>
-      <c r="H139" s="4"/>
-      <c r="I139" s="4"/>
-      <c r="J139" s="4"/>
-      <c r="K139" s="4"/>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G139" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H139" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I139" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="J139" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K139" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A140" s="5"/>
-      <c r="B140" s="4"/>
-      <c r="C140" s="4"/>
-      <c r="D140" s="10"/>
+      <c r="B140" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>294</v>
+      </c>
       <c r="E140" s="4"/>
       <c r="F140" s="4"/>
-      <c r="G140" s="4"/>
-      <c r="H140" s="4"/>
-      <c r="I140" s="4"/>
-      <c r="J140" s="4"/>
-      <c r="K140" s="4"/>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G140" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H140" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I140" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="J140" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K140" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A141" s="5"/>
-      <c r="B141" s="4"/>
-      <c r="C141" s="4"/>
-      <c r="D141" s="10"/>
+      <c r="B141" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>295</v>
+      </c>
       <c r="E141" s="4"/>
       <c r="F141" s="4"/>
-      <c r="G141" s="4"/>
-      <c r="H141" s="4"/>
-      <c r="I141" s="4"/>
-      <c r="J141" s="4"/>
-      <c r="K141" s="4"/>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G141" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I141" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="J141" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K141" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A142" s="5"/>
-      <c r="B142" s="4"/>
-      <c r="C142" s="4"/>
-      <c r="D142" s="10"/>
+      <c r="B142" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
-      <c r="G142" s="4"/>
-      <c r="H142" s="4"/>
-      <c r="I142" s="4"/>
-      <c r="J142" s="4"/>
-      <c r="K142" s="4"/>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G142" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H142" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I142" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="J142" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K142" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A143" s="5"/>
-      <c r="B143" s="4"/>
-      <c r="C143" s="4"/>
-      <c r="D143" s="10"/>
+      <c r="B143" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D143" s="10" t="s">
+        <v>303</v>
+      </c>
       <c r="E143" s="4"/>
       <c r="F143" s="4"/>
-      <c r="G143" s="4"/>
-      <c r="H143" s="4"/>
-      <c r="I143" s="4"/>
-      <c r="J143" s="4"/>
-      <c r="K143" s="4"/>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G143" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I143" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="J143" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K143" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A144" s="5"/>
-      <c r="B144" s="4"/>
-      <c r="C144" s="4"/>
-      <c r="D144" s="10"/>
+      <c r="B144" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D144" s="10" t="s">
+        <v>304</v>
+      </c>
       <c r="E144" s="4"/>
       <c r="F144" s="4"/>
-      <c r="G144" s="4"/>
-      <c r="H144" s="4"/>
-      <c r="I144" s="4"/>
-      <c r="J144" s="4"/>
-      <c r="K144" s="4"/>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G144" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H144" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I144" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="J144" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K144" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A145" s="5"/>
-      <c r="B145" s="4"/>
-      <c r="C145" s="4"/>
-      <c r="D145" s="10"/>
+      <c r="B145" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D145" s="10" t="s">
+        <v>305</v>
+      </c>
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
-      <c r="G145" s="4"/>
-      <c r="H145" s="4"/>
-      <c r="I145" s="4"/>
-      <c r="J145" s="4"/>
-      <c r="K145" s="4"/>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G145" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I145" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="J145" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K145" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A146" s="5"/>
-      <c r="B146" s="4"/>
-      <c r="C146" s="4"/>
-      <c r="D146" s="10"/>
+      <c r="B146" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D146" s="10" t="s">
+        <v>306</v>
+      </c>
       <c r="E146" s="4"/>
       <c r="F146" s="4"/>
-      <c r="G146" s="4"/>
-      <c r="H146" s="4"/>
-      <c r="I146" s="4"/>
-      <c r="J146" s="4"/>
-      <c r="K146" s="4"/>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G146" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H146" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I146" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="J146" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K146" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A147" s="5"/>
-      <c r="B147" s="4"/>
-      <c r="C147" s="4"/>
-      <c r="D147" s="10"/>
+      <c r="B147" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>307</v>
+      </c>
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
-      <c r="G147" s="4"/>
-      <c r="H147" s="4"/>
-      <c r="I147" s="4"/>
-      <c r="J147" s="4"/>
-      <c r="K147" s="4"/>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G147" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I147" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="J147" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K147" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A148" s="5"/>
-      <c r="B148" s="4"/>
-      <c r="C148" s="4"/>
-      <c r="D148" s="10"/>
+      <c r="B148" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D148" s="10" t="s">
+        <v>311</v>
+      </c>
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
-      <c r="G148" s="4"/>
-      <c r="H148" s="4"/>
-      <c r="I148" s="4"/>
-      <c r="J148" s="4"/>
-      <c r="K148" s="4"/>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G148" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H148" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I148" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="J148" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="K148" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A149" s="5"/>
-      <c r="B149" s="4"/>
-      <c r="C149" s="4"/>
-      <c r="D149" s="10"/>
+      <c r="B149" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>312</v>
+      </c>
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
-      <c r="G149" s="4"/>
-      <c r="H149" s="4"/>
-      <c r="I149" s="4"/>
-      <c r="J149" s="4"/>
-      <c r="K149" s="4"/>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G149" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I149" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="J149" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="K149" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A150" s="5"/>
-      <c r="B150" s="4"/>
-      <c r="C150" s="4"/>
-      <c r="D150" s="10"/>
+      <c r="B150" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D150" s="10" t="s">
+        <v>313</v>
+      </c>
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
-      <c r="G150" s="4"/>
-      <c r="H150" s="4"/>
-      <c r="I150" s="4"/>
-      <c r="J150" s="4"/>
-      <c r="K150" s="4"/>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G150" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I150" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="J150" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="K150" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A151" s="5"/>
-      <c r="B151" s="4"/>
-      <c r="C151" s="4"/>
-      <c r="D151" s="10"/>
+      <c r="B151" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D151" s="10" t="s">
+        <v>314</v>
+      </c>
       <c r="E151" s="4"/>
       <c r="F151" s="4"/>
-      <c r="G151" s="4"/>
-      <c r="H151" s="4"/>
-      <c r="I151" s="4"/>
-      <c r="J151" s="4"/>
-      <c r="K151" s="4"/>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G151" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I151" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="J151" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="K151" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A152" s="5"/>
-      <c r="B152" s="4"/>
-      <c r="C152" s="4"/>
-      <c r="D152" s="10"/>
+      <c r="B152" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D152" s="10" t="s">
+        <v>319</v>
+      </c>
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
-      <c r="G152" s="4"/>
-      <c r="H152" s="4"/>
-      <c r="I152" s="4"/>
-      <c r="J152" s="4"/>
-      <c r="K152" s="4"/>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G152" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I152" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J152" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K152" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A153" s="5"/>
-      <c r="B153" s="4"/>
-      <c r="C153" s="4"/>
-      <c r="D153" s="10"/>
+      <c r="B153" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D153" s="10" t="s">
+        <v>320</v>
+      </c>
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
-      <c r="G153" s="4"/>
-      <c r="H153" s="4"/>
-      <c r="I153" s="4"/>
-      <c r="J153" s="4"/>
-      <c r="K153" s="4"/>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G153" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H153" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I153" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J153" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K153" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A154" s="5"/>
-      <c r="B154" s="4"/>
-      <c r="C154" s="4"/>
-      <c r="D154" s="10"/>
+      <c r="B154" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D154" s="10" t="s">
+        <v>321</v>
+      </c>
       <c r="E154" s="4"/>
       <c r="F154" s="4"/>
-      <c r="G154" s="4"/>
-      <c r="H154" s="4"/>
-      <c r="I154" s="4"/>
-      <c r="J154" s="4"/>
-      <c r="K154" s="4"/>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G154" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I154" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J154" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K154" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A155" s="5"/>
-      <c r="B155" s="4"/>
-      <c r="C155" s="4"/>
-      <c r="D155" s="10"/>
+      <c r="B155" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D155" s="10" t="s">
+        <v>324</v>
+      </c>
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
-      <c r="G155" s="4"/>
-      <c r="H155" s="4"/>
-      <c r="I155" s="4"/>
-      <c r="J155" s="4"/>
-      <c r="K155" s="4"/>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G155" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H155" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I155" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J155" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="K155" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A156" s="5"/>
-      <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
-      <c r="D156" s="10"/>
+      <c r="B156" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D156" s="10" t="s">
+        <v>325</v>
+      </c>
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
-      <c r="G156" s="4"/>
-      <c r="H156" s="4"/>
-      <c r="I156" s="4"/>
-      <c r="J156" s="4"/>
-      <c r="K156" s="4"/>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G156" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I156" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J156" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="K156" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" ht="30.75" x14ac:dyDescent="0.2">
       <c r="A157" s="5"/>
-      <c r="B157" s="4"/>
-      <c r="C157" s="4"/>
-      <c r="D157" s="10"/>
+      <c r="B157" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D157" s="10" t="s">
+        <v>326</v>
+      </c>
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
-      <c r="G157" s="4"/>
-      <c r="H157" s="4"/>
-      <c r="I157" s="4"/>
-      <c r="J157" s="4"/>
-      <c r="K157" s="4"/>
+      <c r="G157" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H157" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I157" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J157" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="K157" s="4" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" s="5"/>
@@ -5635,7 +6349,7 @@
       </c>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="2:6" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
@@ -5648,7 +6362,7 @@
       </c>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="2:6" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
@@ -5661,7 +6375,7 @@
       </c>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="2:6" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
       <c r="E5" s="9" t="str">
@@ -5718,7 +6432,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3B7A1D-55E2-4E38-9B0A-883EE9575595}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="50.125" customWidth="1"/>
@@ -5741,7 +6455,7 @@
         <v>Энергетическое оборудование</v>
       </c>
       <c r="C2" t="str" cm="1">
-        <f t="array" ref="C2:D24">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Классификатор!B2:C1000, (Классификатор!B2:B1000&lt;&gt;"") * (Классификатор!C2:C1000&lt;&gt;"")))</f>
+        <f t="array" ref="C2:D32">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Классификатор!B2:C1000, (Классификатор!B2:B1000&lt;&gt;"") * (Классификатор!C2:C1000&lt;&gt;"")))</f>
         <v>Энергетическое оборудование</v>
       </c>
       <c r="D2" t="str">
@@ -5816,7 +6530,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
-        <v>инвентарь и хозяйственные принадлежности</v>
+        <v>Нематериальные компоненты движимого имущества</v>
       </c>
       <c r="C9" t="str">
         <v>Подъёмно-транспортное оборудование</v>
@@ -5827,7 +6541,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
-        <v>нематериальные компоненты движимого имущества</v>
+        <v>Спецтехника</v>
       </c>
       <c r="C10" t="str">
         <v>Строительное и специальное оборудование</v>
@@ -5946,6 +6660,70 @@
       </c>
       <c r="D24" t="str">
         <v>Кассовое оборудование и весы</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C25" t="str">
+        <v>Нематериальные компоненты движимого имущества</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Встроенное и системное программное обеспечение</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C26" t="str">
+        <v>Нематериальные компоненты движимого имущества</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Прикладное программное обеспечение и цифровые лицензии</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C27" t="str">
+        <v>Нематериальные компоненты движимого имущества</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Технологические базы данных и конфигурации</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C28" t="str">
+        <v>Спецтехника</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Строительная спецтехника</v>
+      </c>
+    </row>
+    <row r="29" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C29" t="str">
+        <v>Спецтехника</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Коммунальная спецтехника</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C30" t="str">
+        <v>Спецтехника</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Сельскохозяйственная спецтехника</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C31" t="str">
+        <v>Спецтехника</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Погрузочно-разгрузочная спецтехника</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C32" t="str">
+        <v>Спецтехника</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Грузоподъёмная самоходная спецтехника</v>
       </c>
     </row>
   </sheetData>

--- a/Группы движкимого имущества (параметры).xlsx
+++ b/Группы движкимого имущества (параметры).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Личные папки\Никита Шулин\!Работа\16. Проект (мега-тендер)\9. Мои работы по проекту из августа 2026\Проект - информация и методология\2. Движимое имущество\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\1. ЦОД\Информация от админа\13. Для команды IT\Этап 1 Сбор кабинетных данных\Задачи Султан\2. Движимое имущество\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624EB945-8354-4120-94B1-CB4696349B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D495F8F-FB71-4984-8577-2B504FAA082B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23595" yWindow="1170" windowWidth="21600" windowHeight="12960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Схема движки" sheetId="4" r:id="rId1"/>
@@ -1250,50 +1250,55 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>569628</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>113471</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1">
+        <xdr:cNvPr id="3" name="Рисунок 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E3F11D1-B260-0F17-7052-8F0C78E2EC20}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A17E8679-8B5C-4280-2B0E-0214B55356A8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
-            <a:ext uri="{BEBA8EAE-BF5A-486C-A8C5-ECC9F3942E4B}">
-              <a14:imgProps xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a14:imgLayer r:embed="rId2">
-                  <a14:imgEffect>
-                    <a14:sharpenSoften amount="25000"/>
-                  </a14:imgEffect>
-                </a14:imgLayer>
-              </a14:imgProps>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
+        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="14971428" cy="6628571"/>
+          <a:ext cx="23631525" cy="11134725"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1521,10 +1526,9 @@
     <col min="2" max="2" width="27.375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="30.375" style="11" customWidth="1"/>
-    <col min="5" max="5" width="12.375" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="20.875" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="41.25" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="11" width="41.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.375" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="20.875" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="11" width="41.25" style="2" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
